--- a/premise/data/additional_inventories/lci-ships.xlsx
+++ b/premise/data/additional_inventories/lci-ships.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/Github/premise/premise/data/additional_inventories/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF4F689-4E17-1741-A45E-48F2FB1E57CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269EC39B-B4CF-0948-B675-5D6B79FB850C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20240" yWindow="720" windowWidth="22420" windowHeight="23000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35060" yWindow="-480" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inventories" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="196">
   <si>
     <t>Database</t>
   </si>
@@ -455,6 +455,12 @@
     <t>0.0048 kg CO/kWh shaft power. 38% efficiency. 19.9 MJ/kg methanol.</t>
   </si>
   <si>
+    <t>0.0026 kg NOx/kWh shaft power. 38% efficiency. 19.9 MJ/kg methanol.</t>
+  </si>
+  <si>
+    <t>0.00014 kg PM 2.5/kWh shaft power. 38% efficiency. 19.9 MJ/kg methanol.</t>
+  </si>
+  <si>
     <t>4.9e-7 kg Formaldehyde/kWh shaft power. 38% efficiency. 19.9 MJ/kg methanol.</t>
   </si>
   <si>
@@ -602,6 +608,9 @@
     <t>0.0026 kg NOx/kWh shaft power. 50% efficiency. 43 MJ/kg diesel.</t>
   </si>
   <si>
+    <t>0.00025 kg PM 2.5/kWh shaft power. 50% efficiency. 43 MJ/kg diesel.</t>
+  </si>
+  <si>
     <t>0.00001 kg CH4/kWh shaft power. 50% efficiency. 43 MJ/kg diesel.</t>
   </si>
   <si>
@@ -615,18 +624,6 @@
   </si>
   <si>
     <t>diesel, synthetic</t>
-  </si>
-  <si>
-    <t>Based on the ecoinvent dataset transport, freight, sea, container ship, to which we add an input of diesel and corresponding emissions. We assume a similar tank-to-wake efficiency as that of a martime oil-powered ship.</t>
-  </si>
-  <si>
-    <t>Wartsila reports an emission factor of about 0.7g NOx/MJ methanol: https://www.wartsila.com/insights/article/next-port-of-call-the-methanol-bunkering-station</t>
-  </si>
-  <si>
-    <t>Wartsila reports a 90% PM emission reduction relative to using HFO: https://www.wartsila.com/insights/article/next-port-of-call-the-methanol-bunkering-station</t>
-  </si>
-  <si>
-    <t>80% reduction relative to using HFO at 75% engine load, according to Petzold et al., 2011, dx.doi.org/10.1021/es2021439</t>
   </si>
 </sst>
 </file>
@@ -634,11 +631,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -701,7 +698,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
@@ -709,12 +706,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -723,17 +720,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1084,7 +1081,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1140,7 +1137,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B13" s="13">
         <f>parameters!I7</f>
@@ -1149,7 +1146,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B14" s="13">
         <f>parameters!J7</f>
@@ -1158,7 +1155,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B15" s="13">
         <f>parameters!K7</f>
@@ -1288,7 +1285,7 @@
         <v>41</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I23" s="5">
         <v>5</v>
@@ -1540,7 +1537,7 @@
         <v>23</v>
       </c>
       <c r="E30" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F30" t="s">
         <v>20</v>
@@ -1632,7 +1629,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B41" s="13">
         <f>parameters!I8</f>
@@ -1641,7 +1638,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B42" s="13">
         <f>parameters!J8</f>
@@ -1650,7 +1647,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B43" s="13">
         <f>parameters!K8</f>
@@ -1761,7 +1758,7 @@
     </row>
     <row r="51" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B51" s="17">
         <f>0.11*(B44/B45)/3.6/(1-B41)</f>
@@ -1780,7 +1777,7 @@
         <v>22</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I51">
         <v>5</v>
@@ -2016,7 +2013,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B66" s="13">
         <f>parameters!I6</f>
@@ -2025,7 +2022,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B67" s="13">
         <f>parameters!J6</f>
@@ -2034,7 +2031,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B68" s="13">
         <f>parameters!K6</f>
@@ -2164,7 +2161,7 @@
         <v>58</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I76">
         <v>5</v>
@@ -2620,7 +2617,7 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B97" s="13">
         <f>parameters!I5</f>
@@ -2629,7 +2626,7 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B98" s="13">
         <f>parameters!J5</f>
@@ -2638,7 +2635,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B99" s="13">
         <f>parameters!K5</f>
@@ -2768,7 +2765,7 @@
         <v>68</v>
       </c>
       <c r="H107" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I107">
         <v>5</v>
@@ -2965,8 +2962,8 @@
         <v>24</v>
       </c>
       <c r="B113">
-        <f>(0.7/1000)*19.9*B107</f>
-        <v>9.3613953124999986E-5</v>
+        <f>0.0026*(B107*19.9*B101/3.6)</f>
+        <v>4.2204861111111112E-5</v>
       </c>
       <c r="D113" t="s">
         <v>23</v>
@@ -2978,22 +2975,22 @@
         <v>20</v>
       </c>
       <c r="H113" t="s">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="I113">
         <v>5</v>
       </c>
       <c r="J113" s="6">
         <f t="shared" si="2"/>
-        <v>9.3613953124999986E-5</v>
+        <v>4.2204861111111112E-5</v>
       </c>
       <c r="K113" s="6">
         <f>0.0026*(B107*19.9*B102/3.6)</f>
         <v>3.1653645833333329E-5</v>
       </c>
       <c r="L113" s="6">
-        <f>J113*2</f>
-        <v>1.8722790624999997E-4</v>
+        <f>0.0026*(B107*19.9*B103/3.6)</f>
+        <v>5.2756076388888881E-5</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -3001,8 +2998,8 @@
         <v>62</v>
       </c>
       <c r="B114">
-        <f>0.00695*B107*0.9</f>
-        <v>4.2035554687499993E-5</v>
+        <f>0.00014*(B107*19.9*B101/3.6)</f>
+        <v>2.2725694444444443E-6</v>
       </c>
       <c r="D114" t="s">
         <v>23</v>
@@ -3014,22 +3011,22 @@
         <v>20</v>
       </c>
       <c r="H114" t="s">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="I114">
         <v>5</v>
       </c>
       <c r="J114" s="6">
         <f t="shared" si="2"/>
-        <v>4.2035554687499993E-5</v>
+        <v>2.2725694444444443E-6</v>
       </c>
       <c r="K114" s="6">
         <f>0.00014*(B107*19.9*B102/3.6)</f>
         <v>1.7044270833333331E-6</v>
       </c>
       <c r="L114" s="6">
-        <f>J114*2</f>
-        <v>8.4071109374999985E-5</v>
+        <f>0.00014*(B107*19.9*B103/3.6)</f>
+        <v>2.8407118055555551E-6</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -3050,7 +3047,7 @@
         <v>20</v>
       </c>
       <c r="H115" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I115">
         <v>5</v>
@@ -3150,7 +3147,7 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B126" s="13">
         <f>parameters!I10</f>
@@ -3159,7 +3156,7 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B127" s="13">
         <f>parameters!J10</f>
@@ -3168,7 +3165,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B128" s="13">
         <f>parameters!K10</f>
@@ -3298,7 +3295,7 @@
         <v>110</v>
       </c>
       <c r="H136" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I136">
         <v>5</v>
@@ -3472,7 +3469,7 @@
         <v>20</v>
       </c>
       <c r="H141" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I141">
         <v>5</v>
@@ -3508,7 +3505,7 @@
         <v>20</v>
       </c>
       <c r="H142" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I142">
         <v>5</v>
@@ -3544,7 +3541,7 @@
         <v>20</v>
       </c>
       <c r="H143" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I143">
         <v>5</v>
@@ -3580,7 +3577,7 @@
         <v>20</v>
       </c>
       <c r="H144" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I144">
         <v>5</v>
@@ -3616,7 +3613,7 @@
         <v>20</v>
       </c>
       <c r="H145" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I145">
         <v>5</v>
@@ -3652,7 +3649,7 @@
         <v>20</v>
       </c>
       <c r="H146" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I146">
         <v>5</v>
@@ -3688,7 +3685,7 @@
         <v>20</v>
       </c>
       <c r="H147" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I147">
         <v>5</v>
@@ -3783,7 +3780,7 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B159" s="13">
         <f>parameters!I9</f>
@@ -3792,7 +3789,7 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B160" s="13">
         <f>parameters!J9</f>
@@ -3801,7 +3798,7 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B161" s="13">
         <f>parameters!K9</f>
@@ -3931,7 +3928,7 @@
         <v>116</v>
       </c>
       <c r="H169" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I169">
         <v>5</v>
@@ -4105,7 +4102,7 @@
         <v>20</v>
       </c>
       <c r="H174" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I174">
         <v>5</v>
@@ -4141,7 +4138,7 @@
         <v>20</v>
       </c>
       <c r="H175" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I175">
         <v>5</v>
@@ -4177,7 +4174,7 @@
         <v>20</v>
       </c>
       <c r="H176" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I176">
         <v>5</v>
@@ -4213,7 +4210,7 @@
         <v>20</v>
       </c>
       <c r="H177" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I177">
         <v>5</v>
@@ -4249,7 +4246,7 @@
         <v>20</v>
       </c>
       <c r="H178" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I178">
         <v>5</v>
@@ -4285,7 +4282,7 @@
         <v>20</v>
       </c>
       <c r="H179" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I179">
         <v>5</v>
@@ -4321,7 +4318,7 @@
         <v>20</v>
       </c>
       <c r="H180" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I180">
         <v>5</v>
@@ -4344,7 +4341,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
@@ -4352,7 +4349,7 @@
         <v>11</v>
       </c>
       <c r="B183" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
@@ -4416,7 +4413,7 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B191" s="13">
         <v>0</v>
@@ -4424,7 +4421,7 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B192" s="13">
         <v>0</v>
@@ -4432,7 +4429,7 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B193" s="13">
         <v>0</v>
@@ -4542,14 +4539,14 @@
     </row>
     <row r="201" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B201" s="12">
         <f>0.11*(B194/B195)/46/(1-B191)</f>
         <v>2.0151056763285029E-3</v>
       </c>
       <c r="C201" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E201" t="s">
         <v>9</v>
@@ -4558,10 +4555,10 @@
         <v>17</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H201" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I201">
         <v>5</v>
@@ -4600,7 +4597,7 @@
         <v>43</v>
       </c>
       <c r="H202" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J202" s="11"/>
       <c r="K202" s="11"/>
@@ -4627,7 +4624,7 @@
         <v>49</v>
       </c>
       <c r="H203" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J203" s="11"/>
       <c r="K203" s="11"/>
@@ -4659,7 +4656,7 @@
     </row>
     <row r="205" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B205" s="12">
         <f>B201*3.15</f>
@@ -4675,7 +4672,7 @@
         <v>20</v>
       </c>
       <c r="H205" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I205">
         <v>5</v>
@@ -4695,7 +4692,7 @@
     </row>
     <row r="206" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B206" s="11">
         <f>0.0009*(B201*43*B195/3.6)</f>
@@ -4711,7 +4708,7 @@
         <v>20</v>
       </c>
       <c r="H206" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I206">
         <v>5</v>
@@ -4747,7 +4744,7 @@
         <v>20</v>
       </c>
       <c r="H207" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I207">
         <v>5</v>
@@ -4770,8 +4767,8 @@
         <v>62</v>
       </c>
       <c r="B208" s="11">
-        <f>0.0000163*0.2</f>
-        <v>3.2600000000000001E-6</v>
+        <f>0.00025*(B201*43*B195/3.6)</f>
+        <v>3.0347977053140105E-6</v>
       </c>
       <c r="D208" t="s">
         <v>23</v>
@@ -4783,27 +4780,27 @@
         <v>20</v>
       </c>
       <c r="H208" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I208">
         <v>5</v>
       </c>
       <c r="J208" s="6">
         <f t="shared" si="8"/>
-        <v>3.2600000000000001E-6</v>
+        <v>3.0347977053140105E-6</v>
       </c>
       <c r="K208" s="6">
         <f>0.00025*(B201*43*B196/3.6)</f>
         <v>2.7313179347826089E-6</v>
       </c>
       <c r="L208" s="6">
-        <f>J208*2</f>
-        <v>6.5200000000000003E-6</v>
+        <f>0.00025*(B201*43*B197/3.6)</f>
+        <v>3.3382774758454117E-6</v>
       </c>
     </row>
     <row r="209" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B209" s="11">
         <f>0.00001*(B201*43*B195/3.6)</f>
@@ -4819,7 +4816,7 @@
         <v>20</v>
       </c>
       <c r="H209" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I209">
         <v>5</v>
@@ -4855,7 +4852,7 @@
         <v>20</v>
       </c>
       <c r="H210" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I210">
         <v>5</v>
@@ -4891,7 +4888,7 @@
         <v>20</v>
       </c>
       <c r="H211" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I211">
         <v>5</v>
@@ -4914,7 +4911,7 @@
         <v>3</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.2">
@@ -4922,7 +4919,7 @@
         <v>11</v>
       </c>
       <c r="B214" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.2">
@@ -4986,7 +4983,7 @@
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B222" s="13">
         <f>parameters!I41</f>
@@ -4995,7 +4992,7 @@
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B223" s="13">
         <f>parameters!J41</f>
@@ -5004,7 +5001,7 @@
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B224" s="13">
         <f>parameters!K41</f>
@@ -5115,7 +5112,7 @@
     </row>
     <row r="232" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B232" s="12">
         <f>0.11*(B225/B226)/46/(1-B222)</f>
@@ -5131,10 +5128,10 @@
         <v>17</v>
       </c>
       <c r="G232" s="8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H232" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I232">
         <v>5</v>
@@ -5248,7 +5245,7 @@
         <v>20</v>
       </c>
       <c r="H236" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I236">
         <v>5</v>
@@ -5284,7 +5281,7 @@
         <v>20</v>
       </c>
       <c r="H237" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I237">
         <v>5</v>
@@ -5320,7 +5317,7 @@
         <v>20</v>
       </c>
       <c r="H238" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I238">
         <v>5</v>
@@ -5343,8 +5340,8 @@
         <v>62</v>
       </c>
       <c r="B239" s="11">
-        <f>0.0000163*0.2</f>
-        <v>3.2600000000000001E-6</v>
+        <f>0.00025*(B232*43*B226/3.6)</f>
+        <v>3.0347977053140105E-6</v>
       </c>
       <c r="D239" t="s">
         <v>23</v>
@@ -5356,22 +5353,22 @@
         <v>20</v>
       </c>
       <c r="H239" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I239">
         <v>5</v>
       </c>
       <c r="J239" s="6">
         <f t="shared" si="9"/>
-        <v>3.2600000000000001E-6</v>
+        <v>3.0347977053140105E-6</v>
       </c>
       <c r="K239" s="6">
         <f>0.00025*(B232*43*B227/3.6)</f>
         <v>2.7313179347826089E-6</v>
       </c>
       <c r="L239" s="6">
-        <f>J239*2</f>
-        <v>6.5200000000000003E-6</v>
+        <f>0.00025*(B232*43*B228/3.6)</f>
+        <v>3.3382774758454117E-6</v>
       </c>
     </row>
     <row r="240" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -5392,7 +5389,7 @@
         <v>20</v>
       </c>
       <c r="H240" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I240">
         <v>5</v>
@@ -5428,7 +5425,7 @@
         <v>20</v>
       </c>
       <c r="H241" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I241">
         <v>5</v>
@@ -5464,7 +5461,7 @@
         <v>20</v>
       </c>
       <c r="H242" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I242">
         <v>5</v>
@@ -5487,7 +5484,7 @@
         <v>3</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.2">
@@ -5495,7 +5492,7 @@
         <v>11</v>
       </c>
       <c r="B245" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.2">
@@ -5559,7 +5556,7 @@
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B253" s="13">
         <f>parameters!I72</f>
@@ -5568,7 +5565,7 @@
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B254" s="13">
         <f>parameters!J72</f>
@@ -5577,7 +5574,7 @@
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B255" s="13">
         <f>parameters!K72</f>
@@ -5688,7 +5685,7 @@
     </row>
     <row r="263" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B263" s="12">
         <f>0.11*(B256/B257)/46/(1-B253)</f>
@@ -5704,10 +5701,10 @@
         <v>17</v>
       </c>
       <c r="G263" s="8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H263" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I263">
         <v>5</v>
@@ -5821,7 +5818,7 @@
         <v>20</v>
       </c>
       <c r="H267" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I267">
         <v>5</v>
@@ -5857,7 +5854,7 @@
         <v>20</v>
       </c>
       <c r="H268" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I268">
         <v>5</v>
@@ -5893,7 +5890,7 @@
         <v>20</v>
       </c>
       <c r="H269" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I269">
         <v>5</v>
@@ -5916,8 +5913,8 @@
         <v>62</v>
       </c>
       <c r="B270" s="11">
-        <f>0.0000163*0.2</f>
-        <v>3.2600000000000001E-6</v>
+        <f>0.00025*(B263*43*B257/3.6)</f>
+        <v>3.0347977053140105E-6</v>
       </c>
       <c r="D270" t="s">
         <v>23</v>
@@ -5929,22 +5926,22 @@
         <v>20</v>
       </c>
       <c r="H270" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I270">
         <v>5</v>
       </c>
       <c r="J270" s="6">
         <f t="shared" si="10"/>
-        <v>3.2600000000000001E-6</v>
+        <v>3.0347977053140105E-6</v>
       </c>
       <c r="K270" s="6">
         <f>0.00025*(B263*43*B258/3.6)</f>
         <v>2.7313179347826089E-6</v>
       </c>
       <c r="L270" s="6">
-        <f>J270*2</f>
-        <v>6.5200000000000003E-6</v>
+        <f>0.00025*(B263*43*B259/3.6)</f>
+        <v>3.3382774758454117E-6</v>
       </c>
     </row>
     <row r="271" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -5965,7 +5962,7 @@
         <v>20</v>
       </c>
       <c r="H271" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I271">
         <v>5</v>
@@ -6001,7 +5998,7 @@
         <v>20</v>
       </c>
       <c r="H272" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I272">
         <v>5</v>
@@ -6037,7 +6034,7 @@
         <v>20</v>
       </c>
       <c r="H273" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I273">
         <v>5</v>
@@ -6139,7 +6136,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
         <v>81</v>
@@ -6525,7 +6522,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C15" s="14">
         <f>AVERAGE(D15:E15)</f>
@@ -6636,7 +6633,7 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C22" s="14">
         <f>3.6/(0.166*43)</f>
@@ -6653,7 +6650,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
